--- a/template.xlsx
+++ b/template.xlsx
@@ -503,10 +503,10 @@
     <t>OFFICE</t>
   </si>
   <si>
-    <t>นายสวัสดิ์ เจียมบุนนาค</t>
-  </si>
-  <si>
-    <t>สายรัชนีกร</t>
+    <t/>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>A1</t>
@@ -4412,9 +4412,7 @@
       <c r="Y3" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="Z3" s="105" t="s">
-        <v>96</v>
-      </c>
+      <c r="Z3" s="105"/>
       <c r="AA3" s="105"/>
       <c r="AB3" s="105"/>
       <c r="AC3" s="105"/>
@@ -4424,9 +4422,7 @@
         <v>62</v>
       </c>
       <c r="AG3" s="22"/>
-      <c r="AH3" s="28" t="s">
-        <v>97</v>
-      </c>
+      <c r="AH3" s="28"/>
       <c r="AI3" s="28"/>
       <c r="AJ3" s="27"/>
       <c r="AK3" s="29"/>
@@ -10572,7 +10568,7 @@
       <c r="N1" s="130"/>
       <c r="O1" s="131" t="str">
         <f>+'TIME SHEET'!AH3</f>
-        <v>สายรัชนีกร</v>
+        <v/>
       </c>
       <c r="P1" s="132"/>
       <c r="Q1" s="56"/>
@@ -10612,7 +10608,7 @@
       <c r="H2" s="57"/>
       <c r="I2" s="135" t="str">
         <f>'TIME SHEET'!Z3</f>
-        <v>นายสวัสดิ์ เจียมบุนนาค</v>
+        <v/>
       </c>
       <c r="J2" s="136"/>
       <c r="K2" s="136"/>
@@ -13516,7 +13512,7 @@
       <c r="N1" s="130"/>
       <c r="O1" s="131" t="str">
         <f>+'TIME SHEET'!AH3</f>
-        <v>สายรัชนีกร</v>
+        <v/>
       </c>
       <c r="P1" s="132"/>
       <c r="Q1" s="56"/>
@@ -13561,7 +13557,7 @@
       <c r="H2" s="57"/>
       <c r="I2" s="135" t="str">
         <f>'TIME SHEET'!Z3</f>
-        <v>นายสวัสดิ์ เจียมบุนนาค</v>
+        <v/>
       </c>
       <c r="J2" s="136"/>
       <c r="K2" s="136"/>
